--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251120_201258.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251120_201258.xlsx
@@ -6030,7 +6030,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251120_201258.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251120_201258.xlsx
@@ -6030,7 +6030,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
